--- a/back_end/data/warehouse/에이스기흥.xlsx
+++ b/back_end/data/warehouse/에이스기흥.xlsx
@@ -16,7 +16,7 @@
     <t xml:space="preserve">현 재 고  현 황</t>
   </si>
   <si>
-    <t xml:space="preserve">위탁자 : 8189                                 조회일자 : 2026-05-29</t>
+    <t xml:space="preserve">위탁자 : 8189                                 조회일자 : 2026-06-05</t>
   </si>
   <si>
     <t>수탁품</t>
@@ -88,57 +88,33 @@
     <t>브라질</t>
   </si>
   <si>
-    <t>SMITHFIELD)돈목전지 /est.18079</t>
-  </si>
-  <si>
-    <t>26374371</t>
-  </si>
-  <si>
-    <t>P23,평중/가온</t>
-  </si>
-  <si>
-    <t xml:space="preserve">260225-01371-4041803(23)     -0504-00023</t>
-  </si>
-  <si>
-    <t>MAEU262680070</t>
-  </si>
-  <si>
-    <t>903090003151</t>
-  </si>
-  <si>
-    <t>18079</t>
-  </si>
-  <si>
-    <t>A30301</t>
+    <t>SWIFT)우삼겹양지"UN</t>
+  </si>
+  <si>
+    <t>26377362</t>
+  </si>
+  <si>
+    <t>평중/브루니</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260428-00632-9039075     -0522-00135</t>
+  </si>
+  <si>
+    <t>MAEU267381247</t>
+  </si>
+  <si>
+    <t>803000406788</t>
+  </si>
+  <si>
+    <t>969</t>
+  </si>
+  <si>
+    <t>A10401</t>
   </si>
   <si>
     <t>미국</t>
   </si>
   <si>
-    <t>SWIFT)우삼겹양지"UN</t>
-  </si>
-  <si>
-    <t>26377362</t>
-  </si>
-  <si>
-    <t>평중/브루니</t>
-  </si>
-  <si>
-    <t xml:space="preserve">260428-00632-9039075     -0522-00135</t>
-  </si>
-  <si>
-    <t>MAEU267381247</t>
-  </si>
-  <si>
-    <t>803000406788</t>
-  </si>
-  <si>
-    <t>969</t>
-  </si>
-  <si>
-    <t>A10401</t>
-  </si>
-  <si>
     <t>SWIFT)우삼겹양지"UN /est.969</t>
   </si>
   <si>
@@ -232,6 +208,24 @@
     <t>A20301</t>
   </si>
   <si>
+    <t>SWIFT)우일반갈비"SE</t>
+  </si>
+  <si>
+    <t>26378296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260126-00817-9422913     -0601-00063</t>
+  </si>
+  <si>
+    <t>ONEYRICFPW780300</t>
+  </si>
+  <si>
+    <t>803094601465</t>
+  </si>
+  <si>
+    <t>AB0302</t>
+  </si>
+  <si>
     <t>SWIFT)우부채살"CH</t>
   </si>
   <si>
@@ -247,10 +241,10 @@
     <t>803000406693</t>
   </si>
   <si>
-    <t>617</t>
-  </si>
-  <si>
-    <t>15,412.51</t>
+    <t>545</t>
+  </si>
+  <si>
+    <t>13,724.86</t>
   </si>
 </sst>
 </file>
@@ -639,11 +633,11 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <cols>
-    <col min="1" max="1" width="28.86" customWidth="1"/>
+    <col min="1" max="1" width="27.71" customWidth="1"/>
     <col min="2" max="2" width="9.14" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="3" max="3" width="11.71" customWidth="1"/>
     <col min="4" max="4" width="5" customWidth="1"/>
-    <col min="5" max="5" width="33.86" customWidth="1"/>
+    <col min="5" max="5" width="33" customWidth="1"/>
     <col min="6" max="6" width="18.57" customWidth="1"/>
     <col min="7" max="7" width="13.14" customWidth="1"/>
     <col min="8" max="8" width="7.57" customWidth="1"/>
@@ -653,7 +647,7 @@
     <col min="12" max="12" width="9.57" customWidth="1"/>
     <col min="13" max="13" width="5" customWidth="1"/>
     <col min="14" max="14" width="7" customWidth="1"/>
-    <col min="15" max="15" width="24.86" customWidth="1"/>
+    <col min="15" max="15" width="28.14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
@@ -865,13 +859,13 @@
         <v>33</v>
       </c>
       <c r="J8" s="6">
-        <v>10</v>
+        <v>135</v>
       </c>
       <c r="K8" s="7">
-        <v>171.59999999999999</v>
+        <v>4773.6000000000004</v>
       </c>
       <c r="L8" s="8">
-        <v>46729</v>
+        <v>46806</v>
       </c>
       <c t="s" r="M8" s="5">
         <v>24</v>
@@ -903,19 +897,19 @@
         <v>40</v>
       </c>
       <c t="s" r="H9" s="5">
+        <v>32</v>
+      </c>
+      <c t="s" r="I9" s="5">
         <v>41</v>
       </c>
-      <c t="s" r="I9" s="5">
-        <v>42</v>
-      </c>
       <c r="J9" s="6">
-        <v>135</v>
+        <v>24</v>
       </c>
       <c r="K9" s="7">
-        <v>4773.6000000000004</v>
+        <v>836.25999999999999</v>
       </c>
       <c r="L9" s="8">
-        <v>46806</v>
+        <v>46801</v>
       </c>
       <c t="s" r="M9" s="5">
         <v>24</v>
@@ -926,37 +920,37 @@
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c t="s" r="A10" s="5">
+        <v>35</v>
+      </c>
+      <c t="s" r="B10" s="5">
+        <v>42</v>
+      </c>
+      <c t="s" r="C10" s="5">
         <v>43</v>
-      </c>
-      <c t="s" r="B10" s="5">
-        <v>44</v>
-      </c>
-      <c t="s" r="C10" s="5">
-        <v>45</v>
       </c>
       <c t="s" r="D10" s="5">
         <v>19</v>
       </c>
       <c t="s" r="E10" s="5">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c t="s" r="F10" s="5">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c t="s" r="G10" s="5">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c t="s" r="H10" s="5">
+        <v>32</v>
+      </c>
+      <c t="s" r="I10" s="5">
         <v>41</v>
       </c>
-      <c t="s" r="I10" s="5">
-        <v>49</v>
-      </c>
       <c r="J10" s="6">
-        <v>79</v>
+        <v>2</v>
       </c>
       <c r="K10" s="7">
-        <v>2750.2600000000002</v>
+        <v>70.040000000000006</v>
       </c>
       <c r="L10" s="8">
         <v>46801</v>
@@ -970,40 +964,40 @@
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c t="s" r="A11" s="5">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c t="s" r="B11" s="5">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c t="s" r="C11" s="5">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c t="s" r="D11" s="5">
         <v>19</v>
       </c>
       <c t="s" r="E11" s="5">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c t="s" r="F11" s="5">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c t="s" r="G11" s="5">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c t="s" r="H11" s="5">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c t="s" r="I11" s="5">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J11" s="6">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="K11" s="7">
-        <v>70.040000000000006</v>
+        <v>710.25</v>
       </c>
       <c r="L11" s="8">
-        <v>46801</v>
+        <v>46245</v>
       </c>
       <c t="s" r="M11" s="5">
         <v>24</v>
@@ -1014,46 +1008,44 @@
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c t="s" r="A12" s="5">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c t="s" r="B12" s="5">
-        <v>54</v>
-      </c>
-      <c t="s" r="C12" s="5">
-        <v>45</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="C12" s="5"/>
       <c t="s" r="D12" s="5">
         <v>19</v>
       </c>
       <c t="s" r="E12" s="5">
+        <v>53</v>
+      </c>
+      <c t="s" r="F12" s="5">
+        <v>54</v>
+      </c>
+      <c t="s" r="G12" s="5">
         <v>55</v>
       </c>
-      <c t="s" r="F12" s="5">
+      <c t="s" r="H12" s="5">
         <v>56</v>
       </c>
-      <c t="s" r="G12" s="5">
+      <c t="s" r="I12" s="5">
         <v>57</v>
       </c>
-      <c t="s" r="H12" s="5">
-        <v>41</v>
-      </c>
-      <c t="s" r="I12" s="5">
-        <v>58</v>
-      </c>
       <c r="J12" s="6">
-        <v>25</v>
+        <v>194</v>
       </c>
       <c r="K12" s="7">
-        <v>710.25</v>
+        <v>3710.8600000000001</v>
       </c>
       <c r="L12" s="8">
-        <v>46245</v>
+        <v>46642</v>
       </c>
       <c t="s" r="M12" s="5">
         <v>24</v>
       </c>
       <c t="s" r="N12" s="5">
-        <v>34</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
@@ -1063,7 +1055,9 @@
       <c t="s" r="B13" s="5">
         <v>60</v>
       </c>
-      <c r="C13" s="5"/>
+      <c t="s" r="C13" s="5">
+        <v>37</v>
+      </c>
       <c t="s" r="D13" s="5">
         <v>19</v>
       </c>
@@ -1083,57 +1077,57 @@
         <v>65</v>
       </c>
       <c r="J13" s="6">
-        <v>194</v>
+        <v>60</v>
       </c>
       <c r="K13" s="7">
-        <v>3710.8600000000001</v>
+        <v>1135.8</v>
       </c>
       <c r="L13" s="8">
-        <v>46642</v>
+        <v>46725</v>
       </c>
       <c t="s" r="M13" s="5">
         <v>24</v>
       </c>
       <c t="s" r="N13" s="5">
-        <v>66</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c t="s" r="A14" s="5">
+        <v>66</v>
+      </c>
+      <c t="s" r="B14" s="5">
         <v>67</v>
       </c>
-      <c t="s" r="B14" s="5">
-        <v>68</v>
-      </c>
       <c t="s" r="C14" s="5">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c t="s" r="D14" s="5">
         <v>19</v>
       </c>
       <c t="s" r="E14" s="5">
+        <v>68</v>
+      </c>
+      <c t="s" r="F14" s="5">
         <v>69</v>
       </c>
-      <c t="s" r="F14" s="5">
+      <c t="s" r="G14" s="5">
         <v>70</v>
       </c>
-      <c t="s" r="G14" s="5">
+      <c t="s" r="H14" s="5">
+        <v>64</v>
+      </c>
+      <c t="s" r="I14" s="5">
         <v>71</v>
       </c>
-      <c t="s" r="H14" s="5">
-        <v>72</v>
-      </c>
-      <c t="s" r="I14" s="5">
-        <v>73</v>
-      </c>
       <c r="J14" s="6">
-        <v>130</v>
+        <v>63</v>
       </c>
       <c r="K14" s="7">
-        <v>2460.9000000000001</v>
+        <v>1723.05</v>
       </c>
       <c r="L14" s="8">
-        <v>46725</v>
+        <v>46722</v>
       </c>
       <c t="s" r="M14" s="5">
         <v>24</v>
@@ -1144,28 +1138,28 @@
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c t="s" r="A15" s="5">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c t="s" r="B15" s="5">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c t="s" r="C15" s="5">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c t="s" r="D15" s="5">
         <v>19</v>
       </c>
       <c t="s" r="E15" s="5">
+        <v>74</v>
+      </c>
+      <c t="s" r="F15" s="5">
+        <v>75</v>
+      </c>
+      <c t="s" r="G15" s="5">
         <v>76</v>
       </c>
-      <c t="s" r="F15" s="5">
-        <v>77</v>
-      </c>
-      <c t="s" r="G15" s="5">
-        <v>78</v>
-      </c>
       <c t="s" r="H15" s="5">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c t="s" r="I15" s="5">
         <v>23</v>
@@ -1197,10 +1191,10 @@
       <c r="H16" s="9"/>
       <c r="I16" s="9"/>
       <c t="s" r="J16" s="10">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c t="s" r="K16" s="10">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L16" s="9"/>
       <c r="M16" s="9"/>
